--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260216_201932.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260216_201932.xlsx
@@ -2176,7 +2176,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260216_201932.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260216_201932.xlsx
@@ -4090,7 +4090,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260216_201932.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260216_201932.xlsx
@@ -4090,7 +4090,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260216_201932.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260216_201932.xlsx
@@ -2176,7 +2176,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260216_201932.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260216_201932.xlsx
@@ -2176,7 +2176,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260216_201932.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260216_201932.xlsx
@@ -2176,7 +2176,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260216_201932.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260216_201932.xlsx
@@ -2176,7 +2176,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260216_201932.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260216_201932.xlsx
@@ -2176,7 +2176,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
